--- a/Salidas 9-6-25.xlsx
+++ b/Salidas 9-6-25.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28928"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="570" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{766B9616-C7E5-4BC6-9BEB-D3A5C9768399}"/>
+  <xr:revisionPtr revIDLastSave="571" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ED35037-8BAA-4AAD-A7CB-6538E4736B3E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
   <si>
     <t>SALIDAS DE PREDICACIÓN SEMANA DEL 09/06</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>Casa Flia Alejandro Puppo</t>
-  </si>
-  <si>
-    <t>15,13,12,10</t>
   </si>
   <si>
     <t>Mauro H.</t>
@@ -907,11 +904,11 @@
       <c r="D14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="21">
+        <v>15</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>33</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>34</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>10</v>
@@ -925,13 +922,13 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" s="20">
         <v>37</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" s="18" t="s">
         <v>10</v>

--- a/Salidas 9-6-25.xlsx
+++ b/Salidas 9-6-25.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="571" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ED35037-8BAA-4AAD-A7CB-6538E4736B3E}"/>
+  <xr:revisionPtr revIDLastSave="572" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0F89544-9D3F-3E42-83A8-0EE820FAB4AA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
   <si>
     <t>SALIDAS DE PREDICACIÓN SEMANA DEL 09/06</t>
   </si>
@@ -132,20 +132,20 @@
     <t>Casa Flia Alejandro Puppo</t>
   </si>
   <si>
-    <t>Mauro H.</t>
-  </si>
-  <si>
     <t>Calle 1282 Y 1201</t>
   </si>
   <si>
     <t>Pablo L.</t>
+  </si>
+  <si>
+    <t>Nestor R</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -655,16 +655,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:J18"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="8.7109375" style="1"/>
-    <col min="3" max="3" width="7.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7421875" style="1"/>
+    <col min="3" max="3" width="7.80078125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.6328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="23" t="s">
         <v>0</v>
       </c>
@@ -674,7 +674,7 @@
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -694,7 +694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
@@ -715,7 +715,7 @@
       </c>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
@@ -735,7 +735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
@@ -755,7 +755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
@@ -775,7 +775,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
@@ -796,7 +796,7 @@
       </c>
       <c r="J8" s="17"/>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
@@ -836,7 +836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>23</v>
       </c>
@@ -856,7 +856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
         <v>23</v>
       </c>
@@ -874,7 +874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
         <v>28</v>
       </c>
@@ -894,7 +894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="10" t="s">
         <v>31</v>
       </c>
@@ -908,13 +908,13 @@
         <v>15</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="10" t="s">
         <v>31</v>
       </c>
@@ -922,19 +922,19 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" s="20">
         <v>37</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" s="18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="10" t="s">
         <v>31</v>
       </c>
@@ -944,7 +944,7 @@
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="10" t="s">
         <v>31</v>
       </c>
@@ -954,7 +954,7 @@
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="10" t="s">
         <v>31</v>
       </c>

--- a/Salidas 9-6-25.xlsx
+++ b/Salidas 9-6-25.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29010"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="572" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0F89544-9D3F-3E42-83A8-0EE820FAB4AA}"/>
+  <xr:revisionPtr revIDLastSave="660" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42330CA3-CBA2-4F62-9BB3-CC403F9128D4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
-  <si>
-    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 09/06</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+  <si>
+    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 16/06</t>
   </si>
   <si>
     <t>Dia</t>
@@ -57,7 +57,7 @@
     <t>Lunes</t>
   </si>
   <si>
-    <t>Calle 1149 Y 1122</t>
+    <t>Calle 1149 Y 1146</t>
   </si>
   <si>
     <t>Oscar M.</t>
@@ -75,13 +75,13 @@
     <t>Martes</t>
   </si>
   <si>
-    <t>Calle 1147 Y 1142</t>
+    <t>Calle 1149 Y 1150</t>
   </si>
   <si>
     <t>Horacio F.</t>
   </si>
   <si>
-    <t>Casa Flia Alberto Perezlindo</t>
+    <t>Calle 1149 Y 1134</t>
   </si>
   <si>
     <t>Tobias B.</t>
@@ -90,25 +90,34 @@
     <t>Miercoles</t>
   </si>
   <si>
-    <t>Calle 1155 Y 1130</t>
+    <t>Calle 1149 Y 1124</t>
   </si>
   <si>
     <t>Rodolfo P.</t>
   </si>
   <si>
-    <t>Calle 1211 Y 1286</t>
+    <t>Calle 1282 Y 1213</t>
   </si>
   <si>
     <t>Benjamin S.</t>
   </si>
   <si>
+    <t>Casa Flia Nestor Rolhaiser</t>
+  </si>
+  <si>
+    <t>Nestor R.</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
     <t>Jueves</t>
   </si>
   <si>
-    <t>Casa Flia Sergio Ojeda</t>
-  </si>
-  <si>
-    <t>Calle 1149 Y 1138</t>
+    <t>Casa Flia Elias Espinola</t>
+  </si>
+  <si>
+    <t>Casa Flia Noemi Aguirre</t>
   </si>
   <si>
     <t>Daniel C.</t>
@@ -120,7 +129,7 @@
     <t>Viernes</t>
   </si>
   <si>
-    <t>Casa Flia Andres Frattasi</t>
+    <t>Calle 1149 Y 1128</t>
   </si>
   <si>
     <t>Kevin M.</t>
@@ -132,20 +141,23 @@
     <t>Casa Flia Alejandro Puppo</t>
   </si>
   <si>
+    <t>Casa Flia Marisa Flores</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
     <t>Calle 1282 Y 1201</t>
   </si>
   <si>
     <t>Pablo L.</t>
-  </si>
-  <si>
-    <t>Nestor R</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,8 +182,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -190,8 +208,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -271,11 +295,119 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -338,16 +470,83 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -654,27 +853,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J18"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:J20"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="8.7421875" style="1"/>
-    <col min="3" max="3" width="7.80078125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.6328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B2" s="23" t="s">
+    <row r="2" spans="2:10">
+      <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="2:10">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -694,7 +893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10">
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
@@ -705,7 +904,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="6">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>9</v>
@@ -715,7 +914,7 @@
       </c>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10">
       <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
@@ -735,7 +934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:10">
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
@@ -746,7 +945,7 @@
         <v>14</v>
       </c>
       <c r="E6" s="6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>15</v>
@@ -755,7 +954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10">
       <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
@@ -766,7 +965,7 @@
         <v>16</v>
       </c>
       <c r="E7" s="5">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>17</v>
@@ -775,7 +974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:10">
       <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
@@ -786,7 +985,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="3">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>20</v>
@@ -796,8 +995,8 @@
       </c>
       <c r="J8" s="17"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="2:10">
+      <c r="B9" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="9">
@@ -807,7 +1006,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="5">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>22</v>
@@ -816,158 +1015,189 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="2:10">
+      <c r="B10" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="24">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="7">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="6">
+        <v>41</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="6">
-        <v>66</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="25">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="5">
-        <v>20</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="7">
+    <row r="12" spans="2:10">
+      <c r="B12" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="40">
+        <v>20</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="11">
         <v>0.75</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="6" t="s">
+      <c r="D13" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="47"/>
+      <c r="F13" s="14" t="s">
         <v>17</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="11">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="14">
-        <v>18</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="10" t="s">
+    <row r="14" spans="2:10">
+      <c r="B14" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="27">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="32">
+        <v>8</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="21">
         <v>15</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="12">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="20">
-        <v>37</v>
-      </c>
       <c r="F15" s="13" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G15" s="18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:10">
       <c r="B16" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="C16" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="20">
+        <v>28</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
       <c r="B17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+        <v>34</v>
+      </c>
+      <c r="C17" s="38">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="19">
+        <v>37</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="45"/>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="C19" s="34"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="33"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Salidas 9-6-25.xlsx
+++ b/Salidas 9-6-25.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="660" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42330CA3-CBA2-4F62-9BB3-CC403F9128D4}"/>
+  <xr:revisionPtr revIDLastSave="665" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48FF484E-7F0C-B84B-BD1F-B34B118F8D6E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>SALIDAS DE PREDICACIÓN SEMANA DEL 16/06</t>
   </si>
@@ -66,12 +66,6 @@
     <t>Cong</t>
   </si>
   <si>
-    <t>Calle 1209 Y 1262</t>
-  </si>
-  <si>
-    <t>Joaquin B.</t>
-  </si>
-  <si>
     <t>Martes</t>
   </si>
   <si>
@@ -151,13 +145,16 @@
   </si>
   <si>
     <t>Pablo L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No hay predicación </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,9 +467,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -540,13 +534,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -854,26 +851,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:J20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.80078125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.6328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
-      <c r="B2" s="22" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-    </row>
-    <row r="3" spans="2:10">
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -893,7 +890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
@@ -914,285 +911,277 @@
       </c>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+      <c r="C5" s="9"/>
       <c r="D5" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B6" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="8">
-        <v>34</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10">
-      <c r="B6" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="C6" s="7">
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="6">
         <v>26</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" s="5">
         <v>16</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="7">
         <v>0.39583333333333331</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3">
         <v>7</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="J8" s="17"/>
     </row>
-    <row r="9" spans="2:10">
-      <c r="B9" s="25" t="s">
-        <v>18</v>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="24" t="s">
+        <v>16</v>
       </c>
       <c r="C9" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" s="5">
         <v>59</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
-      <c r="B10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="24">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="23">
         <v>0.66666666666666663</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E10" s="6">
         <v>41</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="C11" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="25">
+      <c r="D11" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="24">
         <v>10</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
-      <c r="B12" s="26" t="s">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="29">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D12" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <v>20</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="F12" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" s="11">
         <v>0.75</v>
       </c>
-      <c r="D13" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="47"/>
+      <c r="D13" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="48"/>
       <c r="F13" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
-      <c r="B14" s="26" t="s">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="31">
+        <v>8</v>
+      </c>
+      <c r="F14" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="27">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D14" s="32" t="s">
+      <c r="G14" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B15" s="10" t="s">
         <v>32</v>
-      </c>
-      <c r="E14" s="32">
-        <v>8</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="B15" s="10" t="s">
-        <v>34</v>
       </c>
       <c r="C15" s="12">
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E15" s="21">
         <v>15</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G15" s="18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="12">
         <v>0.41666666666666669</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E16" s="20">
         <v>28</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="38">
+        <v>32</v>
+      </c>
+      <c r="C17" s="37">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D17" s="39" t="s">
-        <v>38</v>
+      <c r="D17" s="38" t="s">
+        <v>36</v>
       </c>
       <c r="E17" s="19">
         <v>37</v>
       </c>
-      <c r="F17" s="39" t="s">
-        <v>39</v>
+      <c r="F17" s="38" t="s">
+        <v>37</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="45"/>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="C19" s="34"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="33"/>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="C20" s="36"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="40"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="44"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C19" s="33"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="32"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C20" s="35"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Salidas 9-6-25.xlsx
+++ b/Salidas 9-6-25.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29012"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="665" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48FF484E-7F0C-B84B-BD1F-B34B118F8D6E}"/>
+  <xr:revisionPtr revIDLastSave="753" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACB672E3-56C3-4B23-B7A3-5076091A1407}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
-  <si>
-    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 16/06</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+  <si>
+    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 23/06</t>
   </si>
   <si>
     <t>Dia</t>
@@ -66,95 +66,98 @@
     <t>Cong</t>
   </si>
   <si>
+    <t>Calle 1209 Y 1262</t>
+  </si>
+  <si>
+    <t>Joaquin B.</t>
+  </si>
+  <si>
     <t>Martes</t>
   </si>
   <si>
-    <t>Calle 1149 Y 1150</t>
+    <t>Calle 1147 Y 1150</t>
   </si>
   <si>
     <t>Horacio F.</t>
   </si>
   <si>
+    <t xml:space="preserve">Calle 1136 Y 1149 </t>
+  </si>
+  <si>
+    <t>Tobias B.</t>
+  </si>
+  <si>
+    <t>Miercoles</t>
+  </si>
+  <si>
+    <t>Calle 1147 Y 1124</t>
+  </si>
+  <si>
+    <t>Rodolfo P.</t>
+  </si>
+  <si>
+    <t>Calle 1209 Y 1272</t>
+  </si>
+  <si>
+    <t>Benjamin S.</t>
+  </si>
+  <si>
+    <t>Jueves</t>
+  </si>
+  <si>
+    <t>Casa Flia Elias Espinola</t>
+  </si>
+  <si>
+    <t>Dilan F.</t>
+  </si>
+  <si>
+    <t>Calle 1149 Y 1132</t>
+  </si>
+  <si>
+    <t>Daniel C.</t>
+  </si>
+  <si>
+    <t>Predicacion Telefonica Zoom</t>
+  </si>
+  <si>
+    <t>Viernes</t>
+  </si>
+  <si>
     <t>Calle 1149 Y 1134</t>
   </si>
   <si>
-    <t>Tobias B.</t>
-  </si>
-  <si>
-    <t>Miercoles</t>
-  </si>
-  <si>
-    <t>Calle 1149 Y 1124</t>
-  </si>
-  <si>
-    <t>Rodolfo P.</t>
-  </si>
-  <si>
-    <t>Calle 1282 Y 1213</t>
-  </si>
-  <si>
-    <t>Benjamin S.</t>
-  </si>
-  <si>
-    <t>Casa Flia Nestor Rolhaiser</t>
-  </si>
-  <si>
-    <t>Nestor R.</t>
-  </si>
-  <si>
-    <t>G4</t>
-  </si>
-  <si>
-    <t>Jueves</t>
-  </si>
-  <si>
-    <t>Casa Flia Elias Espinola</t>
-  </si>
-  <si>
-    <t>Casa Flia Noemi Aguirre</t>
-  </si>
-  <si>
-    <t>Daniel C.</t>
-  </si>
-  <si>
-    <t>Predicacion Telefonica Zoom</t>
-  </si>
-  <si>
-    <t>Viernes</t>
-  </si>
-  <si>
-    <t>Calle 1149 Y 1128</t>
-  </si>
-  <si>
     <t>Kevin M.</t>
   </si>
   <si>
     <t>Sabado</t>
   </si>
   <si>
-    <t>Casa Flia Alejandro Puppo</t>
-  </si>
-  <si>
-    <t>Casa Flia Marisa Flores</t>
-  </si>
-  <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>Calle 1282 Y 1201</t>
+    <t>Calle 616 Y 512</t>
+  </si>
+  <si>
+    <t>1,2 Y 3</t>
+  </si>
+  <si>
+    <t>Calle 616 Y 504</t>
+  </si>
+  <si>
+    <t>Rafael M.</t>
+  </si>
+  <si>
+    <t>4 Y 5</t>
+  </si>
+  <si>
+    <t>Calle 1209 Y 1256</t>
   </si>
   <si>
     <t>Pablo L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No hay predicación </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,12 +181,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF242424"/>
-      <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -212,7 +209,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -400,11 +397,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -467,10 +479,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -483,18 +491,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -516,9 +512,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -534,16 +527,43 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -851,26 +871,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:J20"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="9.4140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.80078125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.6328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B2" s="46" t="s">
+    <row r="2" spans="2:10">
+      <c r="B2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+    </row>
+    <row r="3" spans="2:10">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -890,7 +910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10">
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
@@ -911,198 +931,206 @@
       </c>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10">
       <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="9">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="D5" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="E5" s="8">
+        <v>34</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
       <c r="B6" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="7">
         <v>0.39583333333333331</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="6">
+        <v>14</v>
+      </c>
+      <c r="E6" s="50">
         <v>26</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10">
       <c r="B7" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" s="5">
         <v>16</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:10">
       <c r="B8" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="7">
         <v>0.39583333333333331</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" s="3">
         <v>7</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="J8" s="17"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="24" t="s">
-        <v>16</v>
+    <row r="9" spans="2:10">
+      <c r="B9" s="22" t="s">
+        <v>18</v>
       </c>
       <c r="C9" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="23">
+    <row r="10" spans="2:10">
+      <c r="B10" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="39">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="40">
+        <v>10</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="41">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="6">
-        <v>41</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="24">
-        <v>10</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>13</v>
+      <c r="D11" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="43">
+        <v>12</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>27</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="29">
-        <v>0.66666666666666663</v>
+    <row r="12" spans="2:10">
+      <c r="B12" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="24">
+        <v>0.75</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="39">
-        <v>20</v>
-      </c>
-      <c r="F12" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="46"/>
+      <c r="F12" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="15">
+        <v>14</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="21">
+        <v>54</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="48"/>
-      <c r="F13" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="26">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="31">
-        <v>8</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="G14" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
       <c r="B15" s="10" t="s">
         <v>32</v>
       </c>
@@ -1110,83 +1138,68 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="21">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="E15" s="20">
+        <v>48</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
       <c r="B16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="20">
-        <v>28</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>27</v>
+      <c r="C16" s="31">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="48">
+        <v>36</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>39</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="37">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="19">
-        <v>37</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="44"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C19" s="33"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="32"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C20" s="35"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
+    <row r="17" spans="2:7">
+      <c r="B17" s="10"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="36"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="37"/>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="26"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="D13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Salidas 9-6-25.xlsx
+++ b/Salidas 9-6-25.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29022"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="753" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACB672E3-56C3-4B23-B7A3-5076091A1407}"/>
+  <xr:revisionPtr revIDLastSave="793" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A05F4766-8481-4545-A984-58B552E4287C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
-  <si>
-    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 23/06</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+  <si>
+    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 30/06</t>
   </si>
   <si>
     <t>Dia</t>
@@ -75,13 +75,13 @@
     <t>Martes</t>
   </si>
   <si>
-    <t>Calle 1147 Y 1150</t>
+    <t>Calle 1147 Y 1152</t>
   </si>
   <si>
     <t>Horacio F.</t>
   </si>
   <si>
-    <t xml:space="preserve">Calle 1136 Y 1149 </t>
+    <t>Calle 1155 Y 1146</t>
   </si>
   <si>
     <t>Tobias B.</t>
@@ -90,13 +90,13 @@
     <t>Miercoles</t>
   </si>
   <si>
-    <t>Calle 1147 Y 1124</t>
+    <t>Calle 1149 Y 1134</t>
   </si>
   <si>
     <t>Rodolfo P.</t>
   </si>
   <si>
-    <t>Calle 1209 Y 1272</t>
+    <t>Calle 1209 Y 1270</t>
   </si>
   <si>
     <t>Benjamin S.</t>
@@ -105,13 +105,13 @@
     <t>Jueves</t>
   </si>
   <si>
-    <t>Casa Flia Elias Espinola</t>
+    <t>Calle 1149 Y 1142</t>
   </si>
   <si>
     <t>Dilan F.</t>
   </si>
   <si>
-    <t>Calle 1149 Y 1132</t>
+    <t>Calle 1282 Y 1209</t>
   </si>
   <si>
     <t>Daniel C.</t>
@@ -123,7 +123,7 @@
     <t>Viernes</t>
   </si>
   <si>
-    <t>Calle 1149 Y 1134</t>
+    <t>Calle 1282 Y 1213</t>
   </si>
   <si>
     <t>Kevin M.</t>
@@ -132,19 +132,10 @@
     <t>Sabado</t>
   </si>
   <si>
-    <t>Calle 616 Y 512</t>
-  </si>
-  <si>
-    <t>1,2 Y 3</t>
-  </si>
-  <si>
-    <t>Calle 616 Y 504</t>
-  </si>
-  <si>
-    <t>Rafael M.</t>
-  </si>
-  <si>
-    <t>4 Y 5</t>
+    <t>Casa Flia Daniel Caseres</t>
+  </si>
+  <si>
+    <t>Miguel C.</t>
   </si>
   <si>
     <t>Calle 1209 Y 1256</t>
@@ -548,9 +539,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -560,10 +548,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -915,7 +906,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="7">
-        <v>0.39583333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>8</v>
@@ -956,12 +947,12 @@
         <v>13</v>
       </c>
       <c r="C6" s="7">
-        <v>0.39583333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="48">
         <v>26</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -982,7 +973,7 @@
         <v>16</v>
       </c>
       <c r="E7" s="5">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>17</v>
@@ -996,13 +987,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="7">
-        <v>0.39583333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>20</v>
@@ -1037,13 +1028,13 @@
         <v>23</v>
       </c>
       <c r="C10" s="39">
-        <v>0.39583333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D10" s="40" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="40">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>25</v>
@@ -1063,7 +1054,7 @@
         <v>26</v>
       </c>
       <c r="E11" s="43">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="F11" s="44" t="s">
         <v>27</v>
@@ -1079,10 +1070,10 @@
       <c r="C12" s="24">
         <v>0.75</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="46"/>
+      <c r="E12" s="45"/>
       <c r="F12" s="25" t="s">
         <v>17</v>
       </c>
@@ -1095,18 +1086,18 @@
         <v>29</v>
       </c>
       <c r="C13" s="11">
-        <v>0.39583333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="15">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="47" t="s">
+      <c r="G13" s="46" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1121,13 +1112,13 @@
         <v>33</v>
       </c>
       <c r="E14" s="21">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:10">
@@ -1135,40 +1126,30 @@
         <v>32</v>
       </c>
       <c r="C15" s="12">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="20">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="31">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="48">
-        <v>36</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="13"/>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="10"/>

--- a/Salidas 9-6-25.xlsx
+++ b/Salidas 9-6-25.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29022"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29101"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="793" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A05F4766-8481-4545-A984-58B552E4287C}"/>
+  <xr:revisionPtr revIDLastSave="837" documentId="11_BAD602ECE08CAD01B2799564B3595F9CDC566F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D51D04F7-F4E3-4DBD-989F-E2C4E9D8EF6E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
-  <si>
-    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 30/06</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="42">
+  <si>
+    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 07/07</t>
   </si>
   <si>
     <t>Dia</t>
@@ -57,7 +57,7 @@
     <t>Lunes</t>
   </si>
   <si>
-    <t>Calle 1149 Y 1146</t>
+    <t>Calle 1149 Y 1148</t>
   </si>
   <si>
     <t>Oscar M.</t>
@@ -81,7 +81,7 @@
     <t>Horacio F.</t>
   </si>
   <si>
-    <t>Calle 1155 Y 1146</t>
+    <t>Calle 1155 Y 1148</t>
   </si>
   <si>
     <t>Tobias B.</t>
@@ -90,28 +90,25 @@
     <t>Miercoles</t>
   </si>
   <si>
-    <t>Calle 1149 Y 1134</t>
+    <t>Calle 1149 Y 1134A</t>
   </si>
   <si>
     <t>Rodolfo P.</t>
   </si>
   <si>
-    <t>Calle 1209 Y 1270</t>
-  </si>
-  <si>
-    <t>Benjamin S.</t>
+    <t>No Hay Salida</t>
   </si>
   <si>
     <t>Jueves</t>
   </si>
   <si>
-    <t>Calle 1149 Y 1142</t>
-  </si>
-  <si>
-    <t>Dilan F.</t>
-  </si>
-  <si>
-    <t>Calle 1282 Y 1209</t>
+    <t>Calle 1147 Y 1142</t>
+  </si>
+  <si>
+    <t>Dylan F.</t>
+  </si>
+  <si>
+    <t>Calle 1209 Y 1264</t>
   </si>
   <si>
     <t>Daniel C.</t>
@@ -123,7 +120,7 @@
     <t>Viernes</t>
   </si>
   <si>
-    <t>Calle 1282 Y 1213</t>
+    <t>Calle 1149 Y 1132</t>
   </si>
   <si>
     <t>Kevin M.</t>
@@ -132,13 +129,31 @@
     <t>Sabado</t>
   </si>
   <si>
-    <t>Casa Flia Daniel Caseres</t>
-  </si>
-  <si>
-    <t>Miguel C.</t>
-  </si>
-  <si>
-    <t>Calle 1209 Y 1256</t>
+    <t>Av Ing Allan Y 611</t>
+  </si>
+  <si>
+    <t>Joel S.</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>Calle 616 Y 506</t>
+  </si>
+  <si>
+    <t>G1 Y G5</t>
+  </si>
+  <si>
+    <t>Calle 616 Y 503</t>
+  </si>
+  <si>
+    <t>Jonatan S.</t>
+  </si>
+  <si>
+    <t>G3 Y G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle 1209 Y 1252 </t>
   </si>
   <si>
     <t>Pablo L.</t>
@@ -551,10 +566,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -872,14 +887,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="3" t="s">
@@ -1007,37 +1022,29 @@
       <c r="B9" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="9">
-        <v>0.66666666666666663</v>
-      </c>
+      <c r="C9" s="9"/>
       <c r="D9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="5">
-        <v>61</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" spans="2:10">
       <c r="B10" s="38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="39">
         <v>0.41666666666666669</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" s="40">
         <v>21</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="23" t="s">
         <v>10</v>
@@ -1045,19 +1052,19 @@
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="41">
         <v>0.66666666666666663</v>
       </c>
       <c r="D11" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="43">
+        <v>63</v>
+      </c>
+      <c r="F11" s="44" t="s">
         <v>26</v>
-      </c>
-      <c r="E11" s="43">
-        <v>57</v>
-      </c>
-      <c r="F11" s="44" t="s">
-        <v>27</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>10</v>
@@ -1065,13 +1072,13 @@
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="24">
         <v>0.75</v>
       </c>
-      <c r="D12" s="50" t="s">
-        <v>28</v>
+      <c r="D12" s="49" t="s">
+        <v>27</v>
       </c>
       <c r="E12" s="45"/>
       <c r="F12" s="25" t="s">
@@ -1083,19 +1090,19 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="11">
         <v>0.41666666666666669</v>
       </c>
       <c r="D13" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="15">
+        <v>14</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>30</v>
-      </c>
-      <c r="E13" s="15">
-        <v>40</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>31</v>
       </c>
       <c r="G13" s="46" t="s">
         <v>10</v>
@@ -1103,61 +1110,83 @@
     </row>
     <row r="14" spans="2:10">
       <c r="B14" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="12">
         <v>0.41666666666666669</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="21">
+        <v>45</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="21">
-        <v>72</v>
-      </c>
-      <c r="F14" s="13" t="s">
+      <c r="G14" s="18" t="s">
         <v>34</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:10">
       <c r="B15" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="12">
-        <v>0.66666666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="20">
+        <v>50</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>36</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="13"/>
+        <v>31</v>
+      </c>
+      <c r="C16" s="31">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="47">
+        <v>48</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="10"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="13"/>
+      <c r="B17" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="31">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="19">
+        <v>36</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" spans="2:7">
       <c r="B18" s="36"/>

--- a/Salidas 9-6-25.xlsx
+++ b/Salidas 9-6-25.xlsx
@@ -629,7 +629,7 @@
         <v>10:00</v>
       </c>
       <c r="C13" t="str">
-        <v>Diagonal 2 Y 506</v>
+        <v>Calle 616 Y 506</v>
       </c>
       <c r="D13" t="str">
         <v>50</v>

--- a/Salidas 9-6-25.xlsx
+++ b/Salidas 9-6-25.xlsx
@@ -629,7 +629,7 @@
         <v>10:00</v>
       </c>
       <c r="C13" t="str">
-        <v>Calle 616 Y 506</v>
+        <v>Diagonal 2 Y 506</v>
       </c>
       <c r="D13" t="str">
         <v>50</v>
